--- a/etf_holdings/2026-10-15_errors.xlsx
+++ b/etf_holdings/2026-10-15_errors.xlsx
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-15 21:41:20</t>
+          <t>2026-10-15 22:12:30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -466,24 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-15 21:42:31</t>
+          <t>2026-10-15 22:13:30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
